--- a/workbooks/12 Final Boss - Championship.xlsx
+++ b/workbooks/12 Final Boss - Championship.xlsx
@@ -2896,7 +2896,7 @@
         <v>89</v>
       </c>
       <c r="D14" s="22" cm="1" t="str">
-        <f t="array" ref="D14">IF(IFERROR(AND(ISNUMBER('R1 Arena'!$F$17),NOT(_xlfn.ISFORMULA('R1 Arena'!$F$17)),INT('R1 Arena'!$F$17)=TODAY()),FALSE),"✔ CLEAR","· not yet")</f>
+        <f t="array" ref="D14">IF(IFERROR(AND(ISNUMBER('R1 Arena'!$F$17),NOT(_xlfn.ISFORMULA('R1 Arena'!$F$17)),'R1 Arena'!$F$17=INT('R1 Arena'!$F$17),'R1 Arena'!$F$17&gt;=DATE(2026,10,12),'R1 Arena'!$F$17&lt;=TODAY()),FALSE),"✔ CLEAR","· not yet")</f>
         <v>· not yet</v>
       </c>
       <c r="E14" s="23"/>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="22" cm="1" t="str">
-        <f t="array" ref="D15">IF('R3 Real-World Mission'!$C$15="Done","✔ CLEAR · self-check","")</f>
+        <f t="array" ref="D15">IFERROR(IF('R3 Real-World Mission'!$C$15="Done","✔ CLEAR · self-check",""),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E15" s="23"/>

--- a/workbooks/12 Final Boss - Championship.xlsx
+++ b/workbooks/12 Final Boss - Championship.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="560">
   <si>
     <t>Challenge</t>
   </si>
@@ -1164,6 +1164,21 @@
     <t>#SPILL!</t>
   </si>
   <si>
+    <t>=SPILL</t>
+  </si>
+  <si>
+    <t>=SPILL(</t>
+  </si>
+  <si>
+    <t>=SPILL()</t>
+  </si>
+  <si>
+    <t>SPILL(</t>
+  </si>
+  <si>
+    <t>SPILL()</t>
+  </si>
+  <si>
     <t>G28</t>
   </si>
   <si>
@@ -1599,16 +1614,19 @@
     <t>HOW TO PLAY</t>
   </si>
   <si>
-    <t>1 · Each stage: read the BRIEFING, then answer WARM-UP, TRAINING and CHALLENGES.</t>
-  </si>
-  <si>
-    <t>2 · Yellow cells are yours: type, pick from a list (Alt+↓), or follow a ▶ ARENA link and do the move there.</t>
-  </si>
-  <si>
-    <t>3 · ✔ CLEAR = right · ✘ = try again · · not yet = drill not done. Stuck? Pick 'Show hint' (5 XP instead of 10).</t>
-  </si>
-  <si>
-    <t>4 · Formatting or hiding drills: press F9 to refresh the check. Tab jumps between yellow cells.</t>
+    <t>1 · Speedrun: stamp START just below (Ctrl+Shift+:) before Round 1 and FINISH after Round 3. Beat par for rank S.</t>
+  </si>
+  <si>
+    <t>2 · Each round: answer its GAUNTLET recall questions (if it has any), then do the MISSIONS in its arena.</t>
+  </si>
+  <si>
+    <t>3 · Yellow cells are yours: type, pick from a list (Alt+↓), or follow a ▶ ARENA link and do the move there.</t>
+  </si>
+  <si>
+    <t>4 · ✔ CLEAR = right · ✘ = try again · · not yet = drill not done. Stuck? Pick 'Show hint' (5 XP instead of 10).</t>
+  </si>
+  <si>
+    <t>5 · Formatting drills: press F9 to refresh the check. Tab jumps between yellow cells.</t>
   </si>
   <si>
     <t>Needs Windows with Microsoft Excel 365 or 2021+ (English). In Protected View, click Enable Editing.</t>
@@ -1677,7 +1695,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>SPEEDRUN · stamp START before Round 1 and FINISH after Round 3</t>
@@ -2399,7 +2417,7 @@
     <tabColor rgb="FF14213D"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2412,7 +2430,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2422,12 +2440,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2437,221 +2455,226 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>525</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>527</v>
       </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="C13" s="9" cm="1" t="str">
-        <f t="array" ref="C13">SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&amp;" / 90"</f>
-        <v>0 / 90</v>
-      </c>
-      <c r="D13" s="10" cm="1" t="str">
-        <f t="array" ref="D13">IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90,"★★★",IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90*0.8,"★★☆",IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90*0.5,"★☆☆","☆☆☆")))</f>
-        <v>☆☆☆</v>
-      </c>
-      <c r="E13" s="9" cm="1" t="str">
-        <f t="array" ref="E13">IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90,"PERFECT",IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90*0.5,"CLEARED",IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;0,"IN PROGRESS","NEW")))</f>
-        <v>NEW</v>
-      </c>
-      <c r="F13" s="11" t="s">
+      <c r="C13" s="6" t="s">
         <v>530</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
-        <f t="array" ref="C14">SUM('R2 Formula Gauntlet'!$G$7:$G$50)&amp;" / 400"</f>
-        <v>0 / 400</v>
+        <f t="array" ref="C14">SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&amp;" / 90"</f>
+        <v>0 / 90</v>
       </c>
       <c r="D14" s="10" cm="1" t="str">
-        <f t="array" ref="D14">IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400,"★★★",IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400*0.8,"★★☆",IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400*0.5,"★☆☆","☆☆☆")))</f>
+        <f t="array" ref="D14">IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90,"★★★",IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90*0.8,"★★☆",IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90*0.5,"★☆☆","☆☆☆")))</f>
         <v>☆☆☆</v>
       </c>
       <c r="E14" s="9" cm="1" t="str">
-        <f t="array" ref="E14">IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400,"PERFECT",IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400*0.5,"CLEARED",IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;0,"IN PROGRESS","NEW")))</f>
+        <f t="array" ref="E14">IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90,"PERFECT",IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;=90*0.5,"CLEARED",IF(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)&gt;0,"IN PROGRESS","NEW")))</f>
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
-        <f t="array" ref="C15">SUM('R3 Real-World Mission'!$G$8:$G$15)&amp;" / 80"</f>
+        <f t="array" ref="C15">SUM('R2 Formula Gauntlet'!$G$7:$G$50)&amp;" / 400"</f>
+        <v>0 / 400</v>
+      </c>
+      <c r="D15" s="10" cm="1" t="str">
+        <f t="array" ref="D15">IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400,"★★★",IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400*0.8,"★★☆",IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400*0.5,"★☆☆","☆☆☆")))</f>
+        <v>☆☆☆</v>
+      </c>
+      <c r="E15" s="9" cm="1" t="str">
+        <f t="array" ref="E15">IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400,"PERFECT",IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;=400*0.5,"CLEARED",IF(SUM('R2 Formula Gauntlet'!$G$7:$G$50)&gt;0,"IN PROGRESS","NEW")))</f>
+        <v>NEW</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="C16" s="9" cm="1" t="str">
+        <f t="array" ref="C16">SUM('R3 Real-World Mission'!$G$8:$G$15)&amp;" / 80"</f>
         <v>0 / 80</v>
       </c>
-      <c r="D15" s="10" cm="1" t="str">
-        <f t="array" ref="D15">IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80,"★★★",IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80*0.8,"★★☆",IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80*0.5,"★☆☆","☆☆☆")))</f>
+      <c r="D16" s="10" cm="1" t="str">
+        <f t="array" ref="D16">IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80,"★★★",IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80*0.8,"★★☆",IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80*0.5,"★☆☆","☆☆☆")))</f>
         <v>☆☆☆</v>
       </c>
-      <c r="E15" s="9" cm="1" t="str">
-        <f t="array" ref="E15">IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80,"PERFECT",IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80*0.5,"CLEARED",IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;0,"IN PROGRESS","NEW")))</f>
+      <c r="E16" s="9" cm="1" t="str">
+        <f t="array" ref="E16">IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80,"PERFECT",IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;=80*0.5,"CLEARED",IF(SUM('R3 Real-World Mission'!$G$8:$G$15)&gt;0,"IN PROGRESS","NEW")))</f>
         <v>NEW</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="B17" s="12" cm="1" t="str">
-        <f t="array" ref="B17">(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)+SUM('R2 Formula Gauntlet'!$G$7:$G$50)+SUM('R3 Real-World Mission'!$G$8:$G$15))&amp;" / 570"</f>
+      <c r="F16" s="11" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="B18" s="12" cm="1" t="str">
+        <f t="array" ref="B18">(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)+SUM('R2 Formula Gauntlet'!$G$7:$G$50)+SUM('R3 Real-World Mission'!$G$8:$G$15))&amp;" / 570"</f>
         <v>0 / 570</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="B18" s="12" cm="1" t="str">
-        <f t="array" ref="B18">_xlfn.LET(_xlpm.p,(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)+SUM('R2 Formula Gauntlet'!$G$7:$G$50)+SUM('R3 Real-World Mission'!$G$8:$G$15))/570,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Start!$C$42),Start!$C$42&lt;=45),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
+    <row r="19" spans="1:6">
+      <c r="A19" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="B19" s="12" cm="1" t="str">
+        <f t="array" ref="B19">_xlfn.LET(_xlpm.p,(SUM('R1 Shortcut Gauntlet'!$G$8:$G$16)+SUM('R2 Formula Gauntlet'!$G$7:$G$50)+SUM('R3 Real-World Mission'!$G$8:$G$15))/570,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Start!$C$28),Start!$C$28&lt;=45),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="B19" s="12" cm="1" t="str">
-        <f t="array" ref="B19">IF(ISNUMBER(Start!$C$42),Start!$C$42&amp;" min (par 45)","—")</f>
+      <c r="C19" s="13" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="B20" s="12" cm="1" t="str">
+        <f t="array" ref="B20">IF(ISNUMBER(Start!$C$28),Start!$C$28&amp;" min (par 45)","—")</f>
         <v>—</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="B20" s="12" cm="1" t="str">
-        <f t="array" ref="B20">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),"All clear! Aim for rank S")</f>
+    <row r="21" spans="1:6">
+      <c r="A21" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="B21" s="12" cm="1" t="str">
+        <f t="array" ref="B21">IFERROR(INDEX($A$14:$A$16,MATCH("☆☆☆",$D$14:$D$16,0))&amp;" "&amp;INDEX($B$14:$B$16,MATCH("☆☆☆",$D$14:$D$16,0)),"All clear! Aim for rank S")</f>
         <v>R1 Shortcut Gauntlet</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="13" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="B40" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="C40" s="14"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="B41" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="C41" s="14"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="B42" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="C42" s="15" cm="1" t="str">
-        <f t="array" ref="C42">IF(OR(C40="",C41=""),"",ROUND(MOD(C41-C40,1)*1440,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="B43" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="C43" s="15">
+    <row r="23" spans="1:6">
+      <c r="A23" s="13" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="B26" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="C26" s="14"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="B27" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="C27" s="14"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="B28" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="C28" s="15" cm="1" t="str">
+        <f t="array" ref="C28">IF(OR(C26="",C27=""),"",ROUND(MOD(C27-C26,1)*1440,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="B29" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="C29" s="15">
         <v>45</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Stamp the time" prompt="Press Ctrl+Shift+: to type the time." sqref="C40"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Stamp the time" prompt="Press Ctrl+Shift+: to type the time." sqref="C41"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Stamp the time" prompt="Press Ctrl+Shift+: to type the time." sqref="C26"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Stamp the time" prompt="Press Ctrl+Shift+: to type the time." sqref="C27"/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F13" location="'R1 Shortcut Gauntlet'!A1" display="Go to R1 Shortcut Gauntlet"/>
-    <hyperlink ref="F14" location="'R2 Formula Gauntlet'!A1" display="Go to R2 Formula Gauntlet"/>
-    <hyperlink ref="F15" location="'R3 Real-World Mission'!A1" display="Go to R3 Real-World Mission"/>
+    <hyperlink ref="F14" location="'R1 Shortcut Gauntlet'!A1" display="Go to R1 Shortcut Gauntlet"/>
+    <hyperlink ref="F15" location="'R2 Formula Gauntlet'!A1" display="Go to R2 Formula Gauntlet"/>
+    <hyperlink ref="F16" location="'R3 Real-World Mission'!A1" display="Go to R3 Real-World Mission"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -7538,7 +7561,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7549,7 +7572,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -7723,7 +7746,7 @@
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="22" cm="1" t="str">
-        <f t="array" ref="D12">IFERROR(_xlfn.LET(_xlpm.a,'R2 Formula Gauntlet'!$C$12,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$16:$E$16),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D12">IFERROR(_xlfn.LET(_xlpm.a,'R2 Formula Gauntlet'!$C$12,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$16:$J$16),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E12" s="23"/>
@@ -7789,7 +7812,7 @@
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="22" cm="1" t="str">
-        <f t="array" ref="D15">IFERROR(_xlfn.LET(_xlpm.a,'R2 Formula Gauntlet'!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$19:$E$19),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D15">IFERROR(_xlfn.LET(_xlpm.a,'R2 Formula Gauntlet'!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$19:$P$19),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E15" s="23"/>
@@ -8200,14 +8223,14 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="20" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="22" cm="1" t="str">
-        <f t="array" ref="D34">IFERROR(_xlfn.LET(_xlpm.a,'R2 Formula Gauntlet'!$C$34,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$38:$G$38),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D34">IFERROR(_xlfn.LET(_xlpm.a,'R2 Formula Gauntlet'!$C$34,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$38:$L$38),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E34" s="23"/>
@@ -8222,10 +8245,10 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="20" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="22" cm="1" t="str">
@@ -8244,10 +8267,10 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="20" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C36" s="21"/>
       <c r="D36" s="22" cm="1" t="str">
@@ -8266,10 +8289,10 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="20" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C37" s="21"/>
       <c r="D37" s="22" cm="1" t="str">
@@ -8288,10 +8311,10 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="20" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C38" s="21"/>
       <c r="D38" s="22" cm="1" t="str">
@@ -8321,7 +8344,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="B41" s="11" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -8352,10 +8375,10 @@
         <v>61</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D43" s="22" cm="1" t="str">
         <f t="array" ref="D43">IF(ISBLANK('R2 Arena'!$O$6),"",IF(NOT(_xlfn.ISFORMULA('R2 Arena'!$O$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('R2 Arena'!$O$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R2 Arena'!$O$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('R2 Arena'!$O$6),ABS('R2 Arena'!$O$6-Key!$C$43)&lt;=1E-9*MAX(1,ABS(Key!$C$43))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIFS")))))</f>
@@ -8376,10 +8399,10 @@
         <v>65</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D44" s="22" cm="1" t="str">
         <f t="array" ref="D44">IF(ISBLANK('R2 Arena'!$O$7),"",IF(NOT(_xlfn.ISFORMULA('R2 Arena'!$O$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('R2 Arena'!$O$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R2 Arena'!$O$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('R2 Arena'!$O$7),ABS('R2 Arena'!$O$7-Key!$C$44)&lt;=1E-9*MAX(1,ABS(Key!$C$44))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIFS")))))</f>
@@ -8400,10 +8423,10 @@
         <v>69</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D45" s="22" cm="1" t="str">
         <f t="array" ref="D45">IF(ISBLANK('R2 Arena'!$O$8),"",IF(NOT(_xlfn.ISFORMULA('R2 Arena'!$O$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('R2 Arena'!$O$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R2 Arena'!$O$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('R2 Arena'!$O$8),'R2 Arena'!$O$8=Key!$C$45),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP")))))</f>
@@ -8424,13 +8447,13 @@
         <v>73</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D46" s="22" cm="1" t="str">
-        <f t="array" ref="D46">IF(ISBLANK('R2 Arena'!$O$9),"",IF(NOT(_xlfn.ISFORMULA('R2 Arena'!$O$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('R2 Arena'!$O$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R2 Arena'!$O$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('R2 Arena'!$O$9),ABS('R2 Arena'!$O$9-Key!$C$46)&lt;=1E-9*MAX(1,ABS(Key!$C$46))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ROUND"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use ROUND and AVERAGEIFS")))))</f>
+        <f t="array" ref="D46">IF(ISBLANK('R2 Arena'!$O$9),"",IF(NOT(_xlfn.ISFORMULA('R2 Arena'!$O$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('R2 Arena'!$O$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R2 Arena'!$O$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('R2 Arena'!$O$9),ABS('R2 Arena'!$O$9-Key!$C$46)&lt;=1E-9*MAX(1,ABS(Key!$C$46))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ROUND"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$9))))),OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$9))))))),"✔ CLEAR","✘ CLOSE · right value, but use ROUND and AVERAGEIF/AVERAGEIFS")))))</f>
         <v/>
       </c>
       <c r="E46" s="23"/>
@@ -8448,10 +8471,10 @@
         <v>77</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D47" s="22" cm="1" t="str">
         <f t="array" ref="D47">IF(ISBLANK('R2 Arena'!$O$10),"",IF(NOT(_xlfn.ISFORMULA('R2 Arena'!$O$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('R2 Arena'!$O$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R2 Arena'!$O$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('R2 Arena'!$O$10),ABS('R2 Arena'!$O$10-Key!$C$47)&lt;=1E-9*MAX(1,ABS(Key!$C$47))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTA"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$10))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTA and UNIQUE")))))</f>
@@ -8472,10 +8495,10 @@
         <v>82</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D48" s="22" cm="1" t="str">
         <f t="array" ref="D48">IF(ISBLANK('R2 Arena'!$O$11),"",IF(NOT(_xlfn.ISFORMULA('R2 Arena'!$O$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('R2 Arena'!$O$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R2 Arena'!$O$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('R2 Arena'!$O$11),ABS('R2 Arena'!$O$11-Key!$C$48)&lt;=1E-9*MAX(1,ABS(Key!$C$48))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EOMONTH"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$11))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MAX"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$O$11)))))),"✔ CLEAR","✘ CLOSE · right value, but use EOMONTH and MAX")))))</f>
@@ -8496,13 +8519,13 @@
         <v>87</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D49" s="22" cm="1" t="str">
-        <f t="array" ref="D49">IF(COUNTA('R2 Arena'!$I$6,'R2 Arena'!$I$7,'R2 Arena'!$I$8,'R2 Arena'!$I$9,'R2 Arena'!$I$10,'R2 Arena'!$I$11,'R2 Arena'!$I$12,'R2 Arena'!$I$13,'R2 Arena'!$I$14,'R2 Arena'!$I$15,'R2 Arena'!$I$16,'R2 Arena'!$I$17,'R2 Arena'!$I$18,'R2 Arena'!$I$19,'R2 Arena'!$I$20,'R2 Arena'!$I$21,'R2 Arena'!$I$22,'R2 Arena'!$I$23,'R2 Arena'!$I$24,'R2 Arena'!$I$25)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('R2 Arena'!$I$6)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$7)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$8)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$9)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$10)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$11)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$12)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$13)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$14)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$15)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$16)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$17)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$18)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$19)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$20)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$21)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$22)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$23)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$24)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$25))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('R2 Arena'!$I$6),ISERROR('R2 Arena'!$I$7),ISERROR('R2 Arena'!$I$8),ISERROR('R2 Arena'!$I$9),ISERROR('R2 Arena'!$I$10),ISERROR('R2 Arena'!$I$11),ISERROR('R2 Arena'!$I$12),ISERROR('R2 Arena'!$I$13),ISERROR('R2 Arena'!$I$14),ISERROR('R2 Arena'!$I$15),ISERROR('R2 Arena'!$I$16),ISERROR('R2 Arena'!$I$17),ISERROR('R2 Arena'!$I$18),ISERROR('R2 Arena'!$I$19),ISERROR('R2 Arena'!$I$20),ISERROR('R2 Arena'!$I$21),ISERROR('R2 Arena'!$I$22),ISERROR('R2 Arena'!$I$23),ISERROR('R2 Arena'!$I$24),ISERROR('R2 Arena'!$I$25)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('R2 Arena'!$I$6),'R2 Arena'!$I$6=Key!$E$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$7),'R2 Arena'!$I$7=Key!$F$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$8),'R2 Arena'!$I$8=Key!$G$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$9),'R2 Arena'!$I$9=Key!$H$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$10),'R2 Arena'!$I$10=Key!$I$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$11),'R2 Arena'!$I$11=Key!$J$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$12),'R2 Arena'!$I$12=Key!$K$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$13),'R2 Arena'!$I$13=Key!$L$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$14),'R2 Arena'!$I$14=Key!$M$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$15),'R2 Arena'!$I$15=Key!$N$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$16),'R2 Arena'!$I$16=Key!$O$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$17),'R2 Arena'!$I$17=Key!$P$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$18),'R2 Arena'!$I$18=Key!$Q$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$19),'R2 Arena'!$I$19=Key!$R$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$20),'R2 Arena'!$I$20=Key!$S$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$21),'R2 Arena'!$I$21=Key!$T$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$22),'R2 Arena'!$I$22=Key!$U$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$23),'R2 Arena'!$I$23=Key!$V$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$24),'R2 Arena'!$I$24=Key!$W$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$25),'R2 Arena'!$I$25=Key!$X$49),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$I$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$I$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF and AND")))))</f>
+        <f t="array" ref="D49">IF(COUNTA('R2 Arena'!$I$6,'R2 Arena'!$I$7,'R2 Arena'!$I$8,'R2 Arena'!$I$9,'R2 Arena'!$I$10,'R2 Arena'!$I$11,'R2 Arena'!$I$12,'R2 Arena'!$I$13,'R2 Arena'!$I$14,'R2 Arena'!$I$15,'R2 Arena'!$I$16,'R2 Arena'!$I$17,'R2 Arena'!$I$18,'R2 Arena'!$I$19,'R2 Arena'!$I$20,'R2 Arena'!$I$21,'R2 Arena'!$I$22,'R2 Arena'!$I$23,'R2 Arena'!$I$24,'R2 Arena'!$I$25)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('R2 Arena'!$I$6)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$7)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$8)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$9)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$10)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$11)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$12)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$13)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$14)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$15)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$16)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$17)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$18)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$19)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$20)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$21)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$22)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$23)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$24)),NOT(_xlfn.ISFORMULA('R2 Arena'!$I$25))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('R2 Arena'!$I$6),ISERROR('R2 Arena'!$I$7),ISERROR('R2 Arena'!$I$8),ISERROR('R2 Arena'!$I$9),ISERROR('R2 Arena'!$I$10),ISERROR('R2 Arena'!$I$11),ISERROR('R2 Arena'!$I$12),ISERROR('R2 Arena'!$I$13),ISERROR('R2 Arena'!$I$14),ISERROR('R2 Arena'!$I$15),ISERROR('R2 Arena'!$I$16),ISERROR('R2 Arena'!$I$17),ISERROR('R2 Arena'!$I$18),ISERROR('R2 Arena'!$I$19),ISERROR('R2 Arena'!$I$20),ISERROR('R2 Arena'!$I$21),ISERROR('R2 Arena'!$I$22),ISERROR('R2 Arena'!$I$23),ISERROR('R2 Arena'!$I$24),ISERROR('R2 Arena'!$I$25)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('R2 Arena'!$I$6),'R2 Arena'!$I$6=Key!$E$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$7),'R2 Arena'!$I$7=Key!$F$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$8),'R2 Arena'!$I$8=Key!$G$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$9),'R2 Arena'!$I$9=Key!$H$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$10),'R2 Arena'!$I$10=Key!$I$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$11),'R2 Arena'!$I$11=Key!$J$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$12),'R2 Arena'!$I$12=Key!$K$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$13),'R2 Arena'!$I$13=Key!$L$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$14),'R2 Arena'!$I$14=Key!$M$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$15),'R2 Arena'!$I$15=Key!$N$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$16),'R2 Arena'!$I$16=Key!$O$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$17),'R2 Arena'!$I$17=Key!$P$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$18),'R2 Arena'!$I$18=Key!$Q$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$19),'R2 Arena'!$I$19=Key!$R$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$20),'R2 Arena'!$I$20=Key!$S$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$21),'R2 Arena'!$I$21=Key!$T$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$22),'R2 Arena'!$I$22=Key!$U$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$23),'R2 Arena'!$I$23=Key!$V$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$24),'R2 Arena'!$I$24=Key!$W$49),FALSE),IFERROR(AND(ISTEXT('R2 Arena'!$I$25),'R2 Arena'!$I$25=Key!$X$49),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$I$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$I$6)))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$I$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF/IFS and AND")))))</f>
         <v/>
       </c>
       <c r="E49" s="23"/>
@@ -8520,10 +8543,10 @@
         <v>92</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D50" s="22" cm="1" t="str">
         <f t="array" ref="D50">IF(ISBLANK('R2 Arena'!$Q$6),"",IF(NOT(_xlfn.ISFORMULA('R2 Arena'!$Q$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('R2 Arena'!$Q$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R2 Arena'!$Q$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('R2 Arena'!$Q$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2001)),COLUMNS(_xlfn.ANCHORARRAY('R2 Arena'!$Q$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2001)),SUM(--(_xlfn.ANCHORARRAY('R2 Arena'!$Q$6)=_xlfn.ANCHORARRAY(Key!$E$2001)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2001))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2001))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('R2 Arena'!$Q$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use FILTER"),"✘ TRY AGAIN"))))</f>
@@ -9349,7 +9372,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9360,7 +9383,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9394,7 +9417,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="11" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -9425,10 +9448,10 @@
         <v>61</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D8" s="22" cm="1" t="str">
         <f t="array" ref="D8">IF(COUNTA('R3 Arena'!$E$6,'R3 Arena'!$E$7,'R3 Arena'!$E$8,'R3 Arena'!$E$9,'R3 Arena'!$E$10,'R3 Arena'!$E$11,'R3 Arena'!$E$12,'R3 Arena'!$E$13,'R3 Arena'!$E$14,'R3 Arena'!$E$15,'R3 Arena'!$E$16,'R3 Arena'!$E$17)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('R3 Arena'!$E$6)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$7)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$8)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$9)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$10)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$11)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$12)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$13)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$14)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$15)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$16)),NOT(_xlfn.ISFORMULA('R3 Arena'!$E$17))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('R3 Arena'!$E$6),ISERROR('R3 Arena'!$E$7),ISERROR('R3 Arena'!$E$8),ISERROR('R3 Arena'!$E$9),ISERROR('R3 Arena'!$E$10),ISERROR('R3 Arena'!$E$11),ISERROR('R3 Arena'!$E$12),ISERROR('R3 Arena'!$E$13),ISERROR('R3 Arena'!$E$14),ISERROR('R3 Arena'!$E$15),ISERROR('R3 Arena'!$E$16),ISERROR('R3 Arena'!$E$17)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('R3 Arena'!$E$6),EXACT('R3 Arena'!$E$6,Key!$E$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$7),EXACT('R3 Arena'!$E$7,Key!$F$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$8),EXACT('R3 Arena'!$E$8,Key!$G$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$9),EXACT('R3 Arena'!$E$9,Key!$H$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$10),EXACT('R3 Arena'!$E$10,Key!$I$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$11),EXACT('R3 Arena'!$E$11,Key!$J$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$12),EXACT('R3 Arena'!$E$12,Key!$K$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$13),EXACT('R3 Arena'!$E$13,Key!$L$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$14),EXACT('R3 Arena'!$E$14,Key!$M$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$15),EXACT('R3 Arena'!$E$15,Key!$N$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$16),EXACT('R3 Arena'!$E$16,Key!$O$51)),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$E$17),EXACT('R3 Arena'!$E$17,Key!$P$51)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"PROPER"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$E$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TRIM"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$E$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use PROPER and TRIM")))))</f>
@@ -9449,10 +9472,10 @@
         <v>65</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D9" s="22" cm="1" t="str">
         <f t="array" ref="D9">IF(COUNTA('R3 Arena'!$F$6,'R3 Arena'!$F$7,'R3 Arena'!$F$8,'R3 Arena'!$F$9,'R3 Arena'!$F$10,'R3 Arena'!$F$11,'R3 Arena'!$F$12,'R3 Arena'!$F$13,'R3 Arena'!$F$14,'R3 Arena'!$F$15,'R3 Arena'!$F$16,'R3 Arena'!$F$17)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('R3 Arena'!$F$6)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$7)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$8)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$9)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$10)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$11)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$12)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$13)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$14)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$15)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$16)),NOT(_xlfn.ISFORMULA('R3 Arena'!$F$17))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('R3 Arena'!$F$6),ISERROR('R3 Arena'!$F$7),ISERROR('R3 Arena'!$F$8),ISERROR('R3 Arena'!$F$9),ISERROR('R3 Arena'!$F$10),ISERROR('R3 Arena'!$F$11),ISERROR('R3 Arena'!$F$12),ISERROR('R3 Arena'!$F$13),ISERROR('R3 Arena'!$F$14),ISERROR('R3 Arena'!$F$15),ISERROR('R3 Arena'!$F$16),ISERROR('R3 Arena'!$F$17)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('R3 Arena'!$F$6),ABS('R3 Arena'!$F$6-Key!$E$52)&lt;=1E-9*MAX(1,ABS(Key!$E$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$7),ABS('R3 Arena'!$F$7-Key!$F$52)&lt;=1E-9*MAX(1,ABS(Key!$F$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$8),ABS('R3 Arena'!$F$8-Key!$G$52)&lt;=1E-9*MAX(1,ABS(Key!$G$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$9),ABS('R3 Arena'!$F$9-Key!$H$52)&lt;=1E-9*MAX(1,ABS(Key!$H$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$10),ABS('R3 Arena'!$F$10-Key!$I$52)&lt;=1E-9*MAX(1,ABS(Key!$I$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$11),ABS('R3 Arena'!$F$11-Key!$J$52)&lt;=1E-9*MAX(1,ABS(Key!$J$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$12),ABS('R3 Arena'!$F$12-Key!$K$52)&lt;=1E-9*MAX(1,ABS(Key!$K$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$13),ABS('R3 Arena'!$F$13-Key!$L$52)&lt;=1E-9*MAX(1,ABS(Key!$L$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$14),ABS('R3 Arena'!$F$14-Key!$M$52)&lt;=1E-9*MAX(1,ABS(Key!$M$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$15),ABS('R3 Arena'!$F$15-Key!$N$52)&lt;=1E-9*MAX(1,ABS(Key!$N$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$16),ABS('R3 Arena'!$F$16-Key!$O$52)&lt;=1E-9*MAX(1,ABS(Key!$O$52))),FALSE),IFERROR(AND(ISNUMBER('R3 Arena'!$F$17),ABS('R3 Arena'!$F$17-Key!$P$52)&lt;=1E-9*MAX(1,ABS(Key!$P$52))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VALUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use VALUE")))))</f>
@@ -9473,10 +9496,10 @@
         <v>69</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D10" s="22" cm="1" t="str">
         <f t="array" ref="D10">IF(COUNTA('R3 Arena'!$G$6,'R3 Arena'!$G$7,'R3 Arena'!$G$8,'R3 Arena'!$G$9,'R3 Arena'!$G$10,'R3 Arena'!$G$11,'R3 Arena'!$G$12,'R3 Arena'!$G$13,'R3 Arena'!$G$14,'R3 Arena'!$G$15,'R3 Arena'!$G$16,'R3 Arena'!$G$17)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('R3 Arena'!$G$6)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$7)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$8)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$9)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$10)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$11)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$12)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$13)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$14)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$15)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$16)),NOT(_xlfn.ISFORMULA('R3 Arena'!$G$17))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('R3 Arena'!$G$6),ISERROR('R3 Arena'!$G$7),ISERROR('R3 Arena'!$G$8),ISERROR('R3 Arena'!$G$9),ISERROR('R3 Arena'!$G$10),ISERROR('R3 Arena'!$G$11),ISERROR('R3 Arena'!$G$12),ISERROR('R3 Arena'!$G$13),ISERROR('R3 Arena'!$G$14),ISERROR('R3 Arena'!$G$15),ISERROR('R3 Arena'!$G$16),ISERROR('R3 Arena'!$G$17)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('R3 Arena'!$G$6),'R3 Arena'!$G$6=Key!$E$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$7),'R3 Arena'!$G$7=Key!$F$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$8),'R3 Arena'!$G$8=Key!$G$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$9),'R3 Arena'!$G$9=Key!$H$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$10),'R3 Arena'!$G$10=Key!$I$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$11),'R3 Arena'!$G$11=Key!$J$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$12),'R3 Arena'!$G$12=Key!$K$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$13),'R3 Arena'!$G$13=Key!$L$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$14),'R3 Arena'!$G$14=Key!$M$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$15),'R3 Arena'!$G$15=Key!$N$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$16),'R3 Arena'!$G$16=Key!$O$53),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$G$17),'R3 Arena'!$G$17=Key!$P$53),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$G$6)))))),IF(ISNUMBER(FIND("$",_xlfn.FORMULATEXT('R3 Arena'!$G$6))),"✔ CLEAR","✘ CLOSE · add $ so it fills correctly (F4)"),"✘ CLOSE · right value, but use XLOOKUP")))))</f>
@@ -9497,10 +9520,10 @@
         <v>73</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D11" s="22" cm="1" t="str">
         <f t="array" ref="D11">IF(ISBLANK('R3 Arena'!$O$6),"",IF(NOT(_xlfn.ISFORMULA('R3 Arena'!$O$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('R3 Arena'!$O$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R3 Arena'!$O$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('R3 Arena'!$O$6),ABS('R3 Arena'!$O$6-Key!$C$54)&lt;=1E-9*MAX(1,ABS(Key!$C$54))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$O$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIFS")))))</f>
@@ -9521,13 +9544,13 @@
         <v>77</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D12" s="22" cm="1" t="str">
-        <f t="array" ref="D12">IF(COUNTA('R3 Arena'!$H$6,'R3 Arena'!$H$7,'R3 Arena'!$H$8,'R3 Arena'!$H$9,'R3 Arena'!$H$10,'R3 Arena'!$H$11,'R3 Arena'!$H$12,'R3 Arena'!$H$13,'R3 Arena'!$H$14,'R3 Arena'!$H$15,'R3 Arena'!$H$16,'R3 Arena'!$H$17)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('R3 Arena'!$H$6)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$7)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$8)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$9)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$10)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$11)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$12)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$13)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$14)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$15)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$16)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$17))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('R3 Arena'!$H$6),ISERROR('R3 Arena'!$H$7),ISERROR('R3 Arena'!$H$8),ISERROR('R3 Arena'!$H$9),ISERROR('R3 Arena'!$H$10),ISERROR('R3 Arena'!$H$11),ISERROR('R3 Arena'!$H$12),ISERROR('R3 Arena'!$H$13),ISERROR('R3 Arena'!$H$14),ISERROR('R3 Arena'!$H$15),ISERROR('R3 Arena'!$H$16),ISERROR('R3 Arena'!$H$17)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('R3 Arena'!$H$6),'R3 Arena'!$H$6=Key!$E$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$7),'R3 Arena'!$H$7=Key!$F$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$8),'R3 Arena'!$H$8=Key!$G$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$9),'R3 Arena'!$H$9=Key!$H$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$10),'R3 Arena'!$H$10=Key!$I$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$11),'R3 Arena'!$H$11=Key!$J$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$12),'R3 Arena'!$H$12=Key!$K$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$13),'R3 Arena'!$H$13=Key!$L$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$14),'R3 Arena'!$H$14=Key!$M$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$15),'R3 Arena'!$H$15=Key!$N$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$16),'R3 Arena'!$H$16=Key!$O$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$17),'R3 Arena'!$H$17=Key!$P$55),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$H$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF")))))</f>
+        <f t="array" ref="D12">IF(COUNTA('R3 Arena'!$H$6,'R3 Arena'!$H$7,'R3 Arena'!$H$8,'R3 Arena'!$H$9,'R3 Arena'!$H$10,'R3 Arena'!$H$11,'R3 Arena'!$H$12,'R3 Arena'!$H$13,'R3 Arena'!$H$14,'R3 Arena'!$H$15,'R3 Arena'!$H$16,'R3 Arena'!$H$17)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('R3 Arena'!$H$6)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$7)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$8)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$9)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$10)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$11)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$12)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$13)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$14)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$15)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$16)),NOT(_xlfn.ISFORMULA('R3 Arena'!$H$17))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('R3 Arena'!$H$6),ISERROR('R3 Arena'!$H$7),ISERROR('R3 Arena'!$H$8),ISERROR('R3 Arena'!$H$9),ISERROR('R3 Arena'!$H$10),ISERROR('R3 Arena'!$H$11),ISERROR('R3 Arena'!$H$12),ISERROR('R3 Arena'!$H$13),ISERROR('R3 Arena'!$H$14),ISERROR('R3 Arena'!$H$15),ISERROR('R3 Arena'!$H$16),ISERROR('R3 Arena'!$H$17)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('R3 Arena'!$H$6),'R3 Arena'!$H$6=Key!$E$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$7),'R3 Arena'!$H$7=Key!$F$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$8),'R3 Arena'!$H$8=Key!$G$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$9),'R3 Arena'!$H$9=Key!$H$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$10),'R3 Arena'!$H$10=Key!$I$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$11),'R3 Arena'!$H$11=Key!$J$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$12),'R3 Arena'!$H$12=Key!$K$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$13),'R3 Arena'!$H$13=Key!$L$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$14),'R3 Arena'!$H$14=Key!$M$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$15),'R3 Arena'!$H$15=Key!$N$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$16),'R3 Arena'!$H$16=Key!$O$55),FALSE),IFERROR(AND(ISTEXT('R3 Arena'!$H$17),'R3 Arena'!$H$17=Key!$P$55),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$H$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$H$6))))))),"✔ CLEAR","✘ CLOSE · right value, but use IF/IFS")))))</f>
         <v/>
       </c>
       <c r="E12" s="23"/>
@@ -9545,13 +9568,13 @@
         <v>82</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D13" s="22" cm="1" t="str">
-        <f t="array" ref="D13">IF(ISBLANK('R3 Arena'!$Q$6),"",IF(NOT(_xlfn.ISFORMULA('R3 Arena'!$Q$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('R3 Arena'!$Q$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R3 Arena'!$Q$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('R3 Arena'!$Q$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101)),COLUMNS(_xlfn.ANCHORARRAY('R3 Arena'!$Q$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101)),SUM(--(_xlfn.ANCHORARRAY('R3 Arena'!$Q$6)=_xlfn.ANCHORARRAY(Key!$E$2101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$Q$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$Q$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT and UNIQUE"),"✘ TRY AGAIN"))))</f>
+        <f t="array" ref="D13">IF(ISBLANK('R3 Arena'!$Q$6),"",IF(NOT(_xlfn.ISFORMULA('R3 Arena'!$Q$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('R3 Arena'!$Q$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('R3 Arena'!$Q$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('R3 Arena'!$Q$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101)),COLUMNS(_xlfn.ANCHORARRAY('R3 Arena'!$Q$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101)),SUM(--(_xlfn.ANCHORARRAY('R3 Arena'!$Q$6)=_xlfn.ANCHORARRAY(Key!$E$2101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101))),FALSE),IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$Q$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORTBY"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$Q$6)))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('R3 Arena'!$Q$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT/SORTBY and UNIQUE"),"✘ TRY AGAIN"))))</f>
         <v/>
       </c>
       <c r="E13" s="23"/>
@@ -9569,10 +9592,10 @@
         <v>87</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D14" s="22" cm="1" t="str">
         <f t="array" ref="D14">IF(IFERROR(AND(OR(CELL("format",'R3 Arena'!$F$6)="C2",CELL("format",'R3 Arena'!$F$6)="C2-"),OR(CELL("format",'R3 Arena'!$F$7)="C2",CELL("format",'R3 Arena'!$F$7)="C2-"),OR(CELL("format",'R3 Arena'!$F$8)="C2",CELL("format",'R3 Arena'!$F$8)="C2-"),OR(CELL("format",'R3 Arena'!$F$9)="C2",CELL("format",'R3 Arena'!$F$9)="C2-"),OR(CELL("format",'R3 Arena'!$F$10)="C2",CELL("format",'R3 Arena'!$F$10)="C2-"),OR(CELL("format",'R3 Arena'!$F$11)="C2",CELL("format",'R3 Arena'!$F$11)="C2-"),OR(CELL("format",'R3 Arena'!$F$12)="C2",CELL("format",'R3 Arena'!$F$12)="C2-"),OR(CELL("format",'R3 Arena'!$F$13)="C2",CELL("format",'R3 Arena'!$F$13)="C2-"),OR(CELL("format",'R3 Arena'!$F$14)="C2",CELL("format",'R3 Arena'!$F$14)="C2-"),OR(CELL("format",'R3 Arena'!$F$15)="C2",CELL("format",'R3 Arena'!$F$15)="C2-"),OR(CELL("format",'R3 Arena'!$F$16)="C2",CELL("format",'R3 Arena'!$F$16)="C2-"),OR(CELL("format",'R3 Arena'!$F$17)="C2",CELL("format",'R3 Arena'!$F$17)="C2-")),FALSE),"✔ CLEAR","· not yet · press F9")</f>
@@ -9593,7 +9616,7 @@
         <v>92</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="22" cm="1" t="str">
@@ -9683,7 +9706,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -9696,86 +9719,86 @@
         <v>6</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="28" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>19</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K5" s="28" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="L5" s="28" t="s">
         <v>19</v>
       </c>
       <c r="Q5" s="28" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="5" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
       <c r="G6" s="29"/>
       <c r="H6" s="29"/>
       <c r="K6" s="5" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="O6" s="29"/>
       <c r="Q6" s="29"/>
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="5" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E7" s="29"/>
       <c r="F7" s="29"/>
       <c r="G7" s="29"/>
       <c r="H7" s="29"/>
       <c r="K7" s="5" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>26</v>
@@ -9783,20 +9806,20 @@
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="5" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E8" s="29"/>
       <c r="F8" s="29"/>
       <c r="G8" s="29"/>
       <c r="H8" s="29"/>
       <c r="K8" s="5" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>29</v>
@@ -9804,20 +9827,20 @@
     </row>
     <row r="9" spans="1:17">
       <c r="B9" s="5" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E9" s="29"/>
       <c r="F9" s="29"/>
       <c r="G9" s="29"/>
       <c r="H9" s="29"/>
       <c r="K9" s="5" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>33</v>
@@ -9825,13 +9848,13 @@
     </row>
     <row r="10" spans="1:17">
       <c r="B10" s="5" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E10" s="29"/>
       <c r="F10" s="29"/>
@@ -9840,13 +9863,13 @@
     </row>
     <row r="11" spans="1:17">
       <c r="B11" s="5" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29"/>
@@ -9855,13 +9878,13 @@
     </row>
     <row r="12" spans="1:17">
       <c r="B12" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="29"/>
@@ -9870,13 +9893,13 @@
     </row>
     <row r="13" spans="1:17">
       <c r="B13" s="5" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E13" s="29"/>
       <c r="F13" s="29"/>
@@ -9885,13 +9908,13 @@
     </row>
     <row r="14" spans="1:17">
       <c r="B14" s="5" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E14" s="29"/>
       <c r="F14" s="29"/>
@@ -9900,13 +9923,13 @@
     </row>
     <row r="15" spans="1:17">
       <c r="B15" s="5" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E15" s="29"/>
       <c r="F15" s="29"/>
@@ -9915,13 +9938,13 @@
     </row>
     <row r="16" spans="1:17">
       <c r="B16" s="5" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="29"/>
@@ -9930,13 +9953,13 @@
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="5" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E17" s="29"/>
       <c r="F17" s="29"/>
@@ -9966,34 +9989,34 @@
   <sheetData>
     <row r="1" spans="1:3" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="B5" s="7" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C5" s="29"/>
     </row>
     <row r="7" spans="1:3">
       <c r="B7" s="7" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="C7" s="30"/>
     </row>
     <row r="9" spans="1:3">
       <c r="B9" s="7" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C9" s="12" cm="1" t="str">
-        <f t="array" ref="C9">Start!$B$18</f>
+        <f t="array" ref="C9">Start!$B$19</f>
         <v>D</v>
       </c>
     </row>
@@ -10005,7 +10028,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="B13" s="33" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -10252,10 +10275,25 @@
         <v>174</v>
       </c>
       <c r="E16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" t="s">
+        <v>156</v>
+      </c>
+      <c r="G16" t="s">
+        <v>157</v>
+      </c>
+      <c r="H16" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="I16" t="s">
+        <v>159</v>
+      </c>
+      <c r="J16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>177</v>
       </c>
@@ -10281,7 +10319,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>187</v>
       </c>
@@ -10307,7 +10345,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>197</v>
       </c>
@@ -10315,10 +10353,43 @@
         <v>198</v>
       </c>
       <c r="E19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" t="s">
+        <v>180</v>
+      </c>
+      <c r="G19" t="s">
+        <v>181</v>
+      </c>
+      <c r="H19" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" t="s">
+        <v>190</v>
+      </c>
+      <c r="J19" t="s">
+        <v>191</v>
+      </c>
+      <c r="K19" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="L19" t="s">
+        <v>183</v>
+      </c>
+      <c r="M19" t="s">
+        <v>184</v>
+      </c>
+      <c r="N19" t="s">
+        <v>192</v>
+      </c>
+      <c r="O19" t="s">
+        <v>193</v>
+      </c>
+      <c r="P19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>201</v>
       </c>
@@ -10344,7 +10415,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>211</v>
       </c>
@@ -10370,7 +10441,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>220</v>
       </c>
@@ -10396,7 +10467,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>230</v>
       </c>
@@ -10422,7 +10493,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>240</v>
       </c>
@@ -10448,7 +10519,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>250</v>
       </c>
@@ -10474,7 +10545,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>259</v>
       </c>
@@ -10500,7 +10571,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>268</v>
       </c>
@@ -10526,7 +10597,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>277</v>
       </c>
@@ -10552,7 +10623,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>286</v>
       </c>
@@ -10578,7 +10649,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>296</v>
       </c>
@@ -10592,7 +10663,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>302</v>
       </c>
@@ -10612,7 +10683,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>310</v>
       </c>
@@ -10638,7 +10709,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
         <v>320</v>
       </c>
@@ -10664,7 +10735,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>330</v>
       </c>
@@ -10690,7 +10761,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>340</v>
       </c>
@@ -10716,7 +10787,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
         <v>350</v>
       </c>
@@ -10742,7 +10813,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
         <v>360</v>
       </c>
@@ -10759,7 +10830,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
         <v>367</v>
       </c>
@@ -10773,152 +10844,167 @@
         <v>370</v>
       </c>
       <c r="G38" t="s">
+        <v>371</v>
+      </c>
+      <c r="H38" t="s">
+        <v>372</v>
+      </c>
+      <c r="I38" t="s">
+        <v>373</v>
+      </c>
+      <c r="J38" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="K38" t="s">
+        <v>374</v>
+      </c>
+      <c r="L38" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B39" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E39" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E40" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F40" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G40" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H40" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I40" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J40" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B41" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="E41" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F41" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="G41" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="H41" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="I41" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J41" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B42" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E42" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F42" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B43" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C43" cm="1">
         <f t="array" ref="C43">SUMIFS('R2 Arena'!$H$6:$H$25,'R2 Arena'!$D$6:$D$25,"West",'R2 Arena'!$F$6:$F$25,"Gadget")</f>
         <v>4500</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B44" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C44" cm="1">
         <f t="array" ref="C44">COUNTIFS('R2 Arena'!$D$6:$D$25,"North",'R2 Arena'!$G$6:$G$25,"&gt;=50")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B45" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C45" cm="1" t="str">
         <f t="array" ref="C45">_xlfn.XLOOKUP("South",'R2 Arena'!$K$6:$K$9,'R2 Arena'!$L$6:$L$9)</f>
         <v>Liam</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C46" cm="1">
         <f t="array" ref="C46">ROUND(AVERAGEIFS('R2 Arena'!$H$6:$H$25,'R2 Arena'!$D$6:$D$25,"East"),0)</f>
         <v>1979.0</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B47" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C47" cm="1">
         <f t="array" ref="C47">COUNTA(_xlfn.UNIQUE('R2 Arena'!$F$6:$F$25))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B48" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C48" cm="1">
         <f t="array" ref="C48">EOMONTH(MAX('R2 Arena'!$C$6:$C$25),0)</f>
@@ -10927,10 +11013,10 @@
     </row>
     <row r="49" spans="1:24">
       <c r="A49" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="E49" cm="1" t="str">
         <f t="array" ref="E49">IF(AND('R2 Arena'!$G$6&gt;=50,'R2 Arena'!$H$6&gt;=2500),"Star","-")</f>
@@ -11015,18 +11101,18 @@
     </row>
     <row r="50" spans="1:24">
       <c r="A50" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="51" spans="1:24">
       <c r="A51" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B51" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E51" cm="1" t="str">
         <f t="array" ref="E51">PROPER(TRIM('R3 Arena'!$B$6))</f>
@@ -11079,10 +11165,10 @@
     </row>
     <row r="52" spans="1:24">
       <c r="A52" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B52" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E52" cm="1">
         <f t="array" ref="E52">VALUE('R3 Arena'!$D$6)</f>
@@ -11135,10 +11221,10 @@
     </row>
     <row r="53" spans="1:24">
       <c r="A53" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B53" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E53" cm="1" t="str">
         <f t="array" ref="E53">_xlfn.XLOOKUP('R3 Arena'!$C$6,'R3 Arena'!$K$6:$K$9,'R3 Arena'!$L$6:$L$9)</f>
@@ -11191,10 +11277,10 @@
     </row>
     <row r="54" spans="1:24">
       <c r="A54" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C54" cm="1">
         <f t="array" ref="C54">SUMPRODUCT(VALUE('R3 Arena'!$D$6:$D$17)*('R3 Arena'!$C$6:$C$17="E"))</f>
@@ -11203,10 +11289,10 @@
     </row>
     <row r="55" spans="1:24">
       <c r="A55" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B55" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="E55" cm="1" t="str">
         <f t="array" ref="E55">IF(VALUE('R3 Arena'!$D$6)&gt;=1000,"Big","")</f>
@@ -11259,29 +11345,29 @@
     </row>
     <row r="56" spans="1:24">
       <c r="A56" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B56" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="57" spans="1:24">
       <c r="A57" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B57" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="58" spans="1:24">
       <c r="A58" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E58" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2001" spans="5:5">
